--- a/stories/arbres/TREE-DIF-035.xlsx
+++ b/stories/arbres/TREE-DIF-035.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Sami est avec papa, au marché. Sami a envie de jouer. papa est là, tout près. On va apprendre : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami écoute papa. Sami entend les mots : corps pas une blague, jouer.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sami va vers la cuisine. Les chaussures font toc toc. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Sami se souvient : corps pas une blague, jouer. Voici le geste : jouer ; pas commenter le corps. On dit merci. papa dit : je suis là. On reste ensemble.</t>
+          <t>Sami va vers la cuisine. Les chaussures font toc toc. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Sami se souvient : corps pas une blague, jouer. Voici le geste : jouer ; pas commenter le corps. On dit merci. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Sami va vers la cuisine. Les chaussures font toc toc. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Sami se souvient : corps pas une blague, jouer. Voici le geste : jouer ; pas commenter le corps. On dit merci.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1858,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Plus rond ou plus mince.</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2031,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : jouer ; pas commenter le corps. Sami respire. Sami retient : corps pas une blague, jouer. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2222,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2389,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi les cubes. On entend un oiseau. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Sami répète tout bas : corps pas une blague, jouer. On attend son tour. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2580,11 @@
         <v>12</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2689,6 +2747,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le matin. Le sol est un peu froid. On dit merci. Cette fin-là est celle de la cuisine, les cubes et le matin. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2914,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3081,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint après la sieste. Une feuille tombe. On souffle doucement. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3248,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3337,6 +3415,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le soir. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, les cubes et le soir. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3582,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3661,6 +3749,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le livre. Ça sent le pain chaud. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Sami répète tout bas : corps pas une blague, jouer. On montre du doigt, sans courir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3940,11 @@
         <v>12</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4009,6 +4107,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le matin. Une feuille tombe. On dit merci. Cette fin-là est celle de la cuisine, le livre et le matin. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4274,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4333,6 +4441,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint après la sieste. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de la cuisine, le livre et après la sieste. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4608,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4657,6 +4775,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le soir. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, le livre et le soir. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4942,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4981,6 +5109,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi la dînette. Le vent est doux. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Sami répète tout bas : corps pas une blague, jouer. On rit un peu. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5167,6 +5300,11 @@
         <v>12</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5329,6 +5467,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le matin. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de la cuisine, la dînette et le matin. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5491,6 +5634,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5653,6 +5801,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint après la sieste. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5815,6 +5968,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5977,6 +6135,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le soir. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, la dînette et le soir. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6139,6 +6302,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6163,7 +6331,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Sami va vers le jardin. La couverture est douce. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Sami se souvient : corps pas une blague, jouer. Voici le geste : jouer ; pas commenter le corps. On souffle doucement. papa dit : je suis là. On reste ensemble.</t>
+          <t>Sami va vers le jardin. La couverture est douce. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Sami se souvient : corps pas une blague, jouer. Voici le geste : jouer ; pas commenter le corps. On souffle doucement. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6301,6 +6469,12 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Sami va vers le jardin. La couverture est douce. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Sami se souvient : corps pas une blague, jouer. Voici le geste : jouer ; pas commenter le corps. On souffle doucement.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6477,6 +6651,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Plus rond ou plus mince.</t>
         </is>
       </c>
     </row>
@@ -6645,6 +6824,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : jouer ; pas commenter le corps. Sami respire. Sami retient : corps pas une blague, jouer. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6831,6 +7015,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6993,6 +7182,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi les cubes. Le sol est un peu froid. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Sami répète tout bas : corps pas une blague, jouer. On attend son tour. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7179,6 +7373,11 @@
         <v>12</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7341,6 +7540,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le matin. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le jardin, les cubes et le matin. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7503,6 +7707,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7665,6 +7874,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint après la sieste. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, les cubes et après la sieste. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7827,6 +8041,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7989,6 +8208,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le soir. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le jardin, les cubes et le soir. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8151,6 +8375,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8313,6 +8542,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le livre. Une feuille tombe. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Sami répète tout bas : corps pas une blague, jouer. On montre du doigt, sans courir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8499,6 +8733,11 @@
         <v>12</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8661,6 +8900,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le matin. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le jardin, le livre et le matin. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8823,6 +9067,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8985,6 +9234,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint après la sieste. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, le livre et après la sieste. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9147,6 +9401,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9309,6 +9568,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le soir. La lumière est claire. On attend son tour. Cette fin-là est celle de le jardin, le livre et le soir. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9471,6 +9735,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9633,6 +9902,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi la dînette. L'eau coule, tout petit bruit. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Sami répète tout bas : corps pas une blague, jouer. On rit un peu. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9819,6 +10093,11 @@
         <v>12</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9981,6 +10260,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le matin. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le jardin, la dînette et le matin. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10143,6 +10427,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10305,6 +10594,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint après la sieste. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, la dînette et après la sieste. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10467,6 +10761,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10629,6 +10928,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le soir. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le jardin, la dînette et le soir. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10791,6 +11095,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10815,7 +11124,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Sami va vers la chambre. On entend un oiseau. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Sami se souvient : corps pas une blague, jouer. Voici le geste : jouer ; pas commenter le corps. On écoute jusqu'au bout. papa dit : je suis là. On reste ensemble.</t>
+          <t>Sami va vers la chambre. On entend un oiseau. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Sami se souvient : corps pas une blague, jouer. Voici le geste : jouer ; pas commenter le corps. On écoute jusqu'au bout. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10953,6 +11262,12 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Sami va vers la chambre. On entend un oiseau. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Sami se souvient : corps pas une blague, jouer. Voici le geste : jouer ; pas commenter le corps. On écoute jusqu'au bout.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11129,6 +11444,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Plus rond ou plus mince.</t>
         </is>
       </c>
     </row>
@@ -11297,6 +11617,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : jouer ; pas commenter le corps. Sami respire. Sami retient : corps pas une blague, jouer. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11483,6 +11808,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11645,6 +11975,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi les cubes. Un vélo passe au loin. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Sami répète tout bas : corps pas une blague, jouer. On attend son tour. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11831,6 +12166,11 @@
         <v>12</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11993,6 +12333,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le matin. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, les cubes et le matin. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12155,6 +12500,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12317,6 +12667,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint après la sieste. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de la chambre, les cubes et après la sieste. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12479,6 +12834,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12641,6 +13001,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le soir. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, les cubes et le soir. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12803,6 +13168,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12965,6 +13335,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le livre. La lumière est claire. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Sami répète tout bas : corps pas une blague, jouer. On montre du doigt, sans courir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13151,6 +13526,11 @@
         <v>12</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13313,6 +13693,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le matin. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, le livre et le matin. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13475,6 +13860,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13637,6 +14027,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint après la sieste. La lumière est claire. On attend son tour. Cette fin-là est celle de la chambre, le livre et après la sieste. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13799,6 +14194,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13961,6 +14361,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le soir. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, le livre et le soir. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14123,6 +14528,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14285,6 +14695,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi la dînette. Il y a des miettes sur la table. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Sami répète tout bas : corps pas une blague, jouer. On rit un peu. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14471,6 +14886,11 @@
         <v>12</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14633,6 +15053,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le matin. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, la dînette et le matin. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14795,6 +15220,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14957,6 +15387,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint après la sieste. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de la chambre, la dînette et après la sieste. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15119,6 +15554,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15281,6 +15721,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le soir. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, la dînette et le soir. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15443,6 +15888,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15461,7 +15911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15478,6 +15928,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-DIF-035.xlsx
+++ b/stories/arbres/TREE-DIF-035.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Sami est avec papa, au marché. Sami a envie de jouer. papa est là, tout près. On va apprendre : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami écoute papa. Sami entend les mots : corps pas une blague, jouer.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1865,6 +1873,7 @@
           <t>narrateur|Que fait-on ? Plus rond ou plus mince.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2036,6 +2045,7 @@
           <t>narrateur|Oui. Voici le geste : jouer ; pas commenter le corps. Sami respire. Sami retient : corps pas une blague, jouer. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2227,6 +2237,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2394,6 +2405,7 @@
           <t>narrateur|Sami a choisi les cubes. On entend un oiseau. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Sami répète tout bas : corps pas une blague, jouer. On attend son tour. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2585,6 +2597,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2752,6 +2765,7 @@
           <t>narrateur|Sami rejoint le matin. Le sol est un peu froid. On dit merci. Cette fin-là est celle de la cuisine, les cubes et le matin. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2919,6 +2933,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3086,6 +3101,7 @@
           <t>narrateur|Sami rejoint après la sieste. Une feuille tombe. On souffle doucement. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3253,6 +3269,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3420,6 +3437,7 @@
           <t>narrateur|Sami rejoint le soir. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, les cubes et le soir. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3587,6 +3605,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3754,6 +3773,7 @@
           <t>narrateur|Sami a choisi le livre. Ça sent le pain chaud. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Sami répète tout bas : corps pas une blague, jouer. On montre du doigt, sans courir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3945,6 +3965,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4112,6 +4133,7 @@
           <t>narrateur|Sami rejoint le matin. Une feuille tombe. On dit merci. Cette fin-là est celle de la cuisine, le livre et le matin. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4279,6 +4301,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4446,6 +4469,7 @@
           <t>narrateur|Sami rejoint après la sieste. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de la cuisine, le livre et après la sieste. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4613,6 +4637,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4780,6 +4805,7 @@
           <t>narrateur|Sami rejoint le soir. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, le livre et le soir. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4947,6 +4973,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5114,6 +5141,7 @@
           <t>narrateur|Sami a choisi la dînette. Le vent est doux. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Sami répète tout bas : corps pas une blague, jouer. On rit un peu. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5305,6 +5333,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5472,6 +5501,7 @@
           <t>narrateur|Sami rejoint le matin. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de la cuisine, la dînette et le matin. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5639,6 +5669,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5806,6 +5837,7 @@
           <t>narrateur|Sami rejoint après la sieste. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5973,6 +6005,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6140,6 +6173,7 @@
           <t>narrateur|Sami rejoint le soir. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, la dînette et le soir. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6307,6 +6341,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6475,6 +6510,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6658,6 +6694,7 @@
           <t>narrateur|Que fait-on ? Plus rond ou plus mince.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6829,6 +6866,7 @@
           <t>narrateur|Oui. Voici le geste : jouer ; pas commenter le corps. Sami respire. Sami retient : corps pas une blague, jouer. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7020,6 +7058,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7187,6 +7226,7 @@
           <t>narrateur|Sami a choisi les cubes. Le sol est un peu froid. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Sami répète tout bas : corps pas une blague, jouer. On attend son tour. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7378,6 +7418,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7545,6 +7586,7 @@
           <t>narrateur|Sami rejoint le matin. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le jardin, les cubes et le matin. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7712,6 +7754,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7879,6 +7922,7 @@
           <t>narrateur|Sami rejoint après la sieste. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, les cubes et après la sieste. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8046,6 +8090,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8213,6 +8258,7 @@
           <t>narrateur|Sami rejoint le soir. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le jardin, les cubes et le soir. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8380,6 +8426,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8547,6 +8594,7 @@
           <t>narrateur|Sami a choisi le livre. Une feuille tombe. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Sami répète tout bas : corps pas une blague, jouer. On montre du doigt, sans courir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8738,6 +8786,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8905,6 +8954,7 @@
           <t>narrateur|Sami rejoint le matin. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le jardin, le livre et le matin. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9072,6 +9122,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9239,6 +9290,7 @@
           <t>narrateur|Sami rejoint après la sieste. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, le livre et après la sieste. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9406,6 +9458,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9573,6 +9626,7 @@
           <t>narrateur|Sami rejoint le soir. La lumière est claire. On attend son tour. Cette fin-là est celle de le jardin, le livre et le soir. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9740,6 +9794,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9907,6 +9962,7 @@
           <t>narrateur|Sami a choisi la dînette. L'eau coule, tout petit bruit. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Sami répète tout bas : corps pas une blague, jouer. On rit un peu. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10098,6 +10154,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10265,6 +10322,7 @@
           <t>narrateur|Sami rejoint le matin. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le jardin, la dînette et le matin. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10432,6 +10490,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10599,6 +10658,7 @@
           <t>narrateur|Sami rejoint après la sieste. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, la dînette et après la sieste. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10766,6 +10826,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10933,6 +10994,7 @@
           <t>narrateur|Sami rejoint le soir. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le jardin, la dînette et le soir. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11100,6 +11162,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11268,6 +11331,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11451,6 +11515,7 @@
           <t>narrateur|Que fait-on ? Plus rond ou plus mince.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11622,6 +11687,7 @@
           <t>narrateur|Oui. Voici le geste : jouer ; pas commenter le corps. Sami respire. Sami retient : corps pas une blague, jouer. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11813,6 +11879,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11980,6 +12047,7 @@
           <t>narrateur|Sami a choisi les cubes. Un vélo passe au loin. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Sami répète tout bas : corps pas une blague, jouer. On attend son tour. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12171,6 +12239,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12338,6 +12407,7 @@
           <t>narrateur|Sami rejoint le matin. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, les cubes et le matin. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12505,6 +12575,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12672,6 +12743,7 @@
           <t>narrateur|Sami rejoint après la sieste. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de la chambre, les cubes et après la sieste. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12839,6 +12911,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13006,6 +13079,7 @@
           <t>narrateur|Sami rejoint le soir. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, les cubes et le soir. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13173,6 +13247,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13340,6 +13415,7 @@
           <t>narrateur|Sami a choisi le livre. La lumière est claire. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Sami répète tout bas : corps pas une blague, jouer. On montre du doigt, sans courir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13531,6 +13607,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13698,6 +13775,7 @@
           <t>narrateur|Sami rejoint le matin. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, le livre et le matin. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13865,6 +13943,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14032,6 +14111,7 @@
           <t>narrateur|Sami rejoint après la sieste. La lumière est claire. On attend son tour. Cette fin-là est celle de la chambre, le livre et après la sieste. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14199,6 +14279,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14366,6 +14447,7 @@
           <t>narrateur|Sami rejoint le soir. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, le livre et le soir. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14533,6 +14615,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14700,6 +14783,7 @@
           <t>narrateur|Sami a choisi la dînette. Il y a des miettes sur la table. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Sami répète tout bas : corps pas une blague, jouer. On rit un peu. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14891,6 +14975,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15058,6 +15143,7 @@
           <t>narrateur|Sami rejoint le matin. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, la dînette et le matin. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15225,6 +15311,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15392,6 +15479,7 @@
           <t>narrateur|Sami rejoint après la sieste. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de la chambre, la dînette et après la sieste. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15559,6 +15647,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15726,6 +15815,7 @@
           <t>narrateur|Sami rejoint le soir. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, la dînette et le soir. Sami a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Sami a entendu : corps pas une blague, jouer. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15893,6 +15983,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15911,7 +16002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15935,6 +16026,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15949,7 +16054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16136,6 +16241,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-DIF-035.xlsx
+++ b/stories/arbres/TREE-DIF-035.xlsx
@@ -1197,12 +1197,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Après la pluie, la maison sent le savon. Dans la salle de bain, le carrelage brille. Une goutte tombe encore du robinet. Deux poupées attendent sur le rebord tiède. La poupée de coton a le ventre tout rond. La poupée de bois a les jambes toutes minces. Tu les as sorties du panier ? Oui. Je veux leur donner un bain. Les deux, Chouchou ? Les deux. En ce moment, Chouchou touche le savon. Il sent la lavande, encore un peu froid. Elles ne se ressemblent pas. On les emmène toutes les deux. Le savon, le gobelet, et la serviette. Merci, tu as ouvert le robinet. On prépare, d'abord.</t>
+          <t>Après la pluie, la maison sent le savon. Dans la salle de bain, le carrelage brille. Une goutte tombe encore du robinet. Tu l'entends, Chouchou ? Oui, le robinet. Deux poupées attendent sur le rebord tiède. La poupée de coton a le ventre tout rond. La poupée de bois a les jambes toutes minces. Tu les as sorties du panier ? Oui. Je veux leur donner un bain. Les deux, Chouchou ? Les deux. En ce moment, Chouchou touche le savon. Il sent la lavande, encore un peu froid. Elles ne se ressemblent pas. On les emmène toutes les deux. Le savon, le gobelet, et la serviette. Merci, tu as sorti les deux. On prépare, d'abord.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Après la pluie, la maison sent le savon. Dans la salle de bain, le carrelage brille. Une goutte tombe encore du robinet. Deux poupées attendent sur le rebord tiède. La poupée de coton a le ventre tout rond. La poupée de bois a les jambes toutes minces. Tu les as sorties du panier ? Oui. Je veux leur donner un bain. Les deux, Chouchou ? Les deux. En ce moment, Chouchou touche le savon. Il sent la lavande, encore un peu froid. Elles ne se ressemblent pas. On les emmène toutes les deux. Le savon, le gobelet, et la serviette. Merci, tu as ouvert le robinet. On prépare, d'abord.</t>
+          <t>Après la pluie, la maison sent le savon. Dans la salle de bain, le carrelage brille. Une goutte tombe encore du robinet. Tu l'entends, Chouchou ? Oui, le robinet. Deux poupées attendent sur le rebord tiède. La poupée de coton a le ventre tout rond. La poupée de bois a les jambes toutes minces. Tu les as sorties du panier ? Oui. Je veux leur donner un bain. Les deux, Chouchou ? Les deux. En ce moment, Chouchou touche le savon. Il sent la lavande, encore un peu froid. Elles ne se ressemblent pas. On les emmène toutes les deux. Le savon, le gobelet, et la serviette. Merci, tu as sorti les deux. On prépare, d'abord.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1340,10 +1340,12 @@
           <t>narrateur|Après la pluie, la maison sent le savon.
 narrateur|Dans la salle de bain, le carrelage brille.
 narrateur|Une goutte tombe encore du robinet.
+maman|Tu l'entends, Chouchou ?
+enfant-f|Oui, le robinet.
 narrateur|Deux poupées attendent sur le rebord tiède.
 narrateur|La poupée de coton a le ventre tout rond.
 narrateur|La poupée de bois a les jambes toutes minces.
-maman|Tu les as sorties du panier ?
+papa|Tu les as sorties du panier ?
 enfant-f|Oui.
 enfant-f|Je veux leur donner un bain.
 papa|Les deux, Chouchou ?
@@ -1353,7 +1355,7 @@
 enfant-f|Elles ne se ressemblent pas.
 papa|On les emmène toutes les deux.
 maman|Le savon, le gobelet, et la serviette.
-papa|Merci, tu as ouvert le robinet.
+papa|Merci, tu as sorti les deux.
 enfant-f|On prépare, d'abord.</t>
         </is>
       </c>
@@ -16466,7 +16468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16509,6 +16511,13 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
